--- a/docs/design-vi/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: tạo カテゴリ6 và bổ sung 5 ca. 044〜047 vốn đã có ở bản tiếng Nhật nhưng chưa được dịch (cộng dồn nhiều lịch sử cùng ngày, hủy đăng ký vào số bản giảm, đổi cửa hàng bán, phân trang 15 dòng/trang khớp với PDF). 048＝giới hạn đối tượng tổng hợp chỉ bản giấy (#56410): điều kiện cũ "bản điện tử chỉ tổng hợp khi đã duyệt" đã bị bỏ vì nằm gọn trong giới hạn này; có kèm bước đối chiếu với SCR-028 vì hai màn giữ điều kiện riêng</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ59"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11040,20 +11098,20 @@
       <c r="BP38" s="10" t="n"/>
       <c r="BQ38" s="11" t="n"/>
     </row>
-    <row r="39" ht="160" customHeight="1">
+    <row r="39" ht="176" customHeight="1">
       <c r="A39" s="44" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-024</t>
+          <t>ACSMS-TC-029-044</t>
         </is>
       </c>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị cột 委託</t>
+          <t>Cộng dồn nhiều lịch sử trong cùng ngày (1→3→5 thành hiện tại 1/mới 5/tăng 4)</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -11063,7 +11121,7 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại 販売店 có 委託区分 là 日農委託・振込・その他</t>
+・Tồn tại lịch sử cùng một người đọc đổi số bản nhiều lần trong cùng ngày áp dụng theo 1→3→5 (từ 2 bản ghi trở lên trong cùng ngày)</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -11088,7 +11146,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
 </t>
           </r>
           <r>
@@ -11105,7 +11163,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận cột 委託 của dòng chi tiết</t>
+            <t>Kiểm tra dòng chi tiết của cửa hàng bán tương ứng</t>
           </r>
         </is>
       </c>
@@ -11148,15 +11206,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・販売店 có 委託区分 là 日農委託（`itaku_kubun=2`）hiển thị「委託」ở cột 委託
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・販売店 có 委託区分 là 振込（1）・その他（9）hiển thị cột 委託 để trống</t>
+            <t xml:space="preserve">・Biến động của người đọc tương ứng được tính vào **1 dòng** (cộng dồn chứ không phải 2 dòng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Số bản hiện tại **1**, số bản mới **5**, số bản tăng **4**, số bản giảm **0**</t>
           </r>
         </is>
       </c>
@@ -11202,7 +11260,11 @@
       <c r="BH39" s="45" t="inlineStr"/>
       <c r="BI39" s="10" t="n"/>
       <c r="BJ39" s="11" t="n"/>
-      <c r="BK39" s="46" t="inlineStr"/>
+      <c r="BK39" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
       <c r="BL39" s="10" t="n"/>
       <c r="BM39" s="10" t="n"/>
       <c r="BN39" s="10" t="n"/>
@@ -11210,20 +11272,20 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="144" customHeight="1">
+    <row r="40" ht="112" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-025</t>
+          <t>ACSMS-TC-029-045</t>
         </is>
       </c>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị 販売店 miễn thuế</t>
+          <t>Hủy đăng ký (…→0) được phản ánh vào số bản giảm</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -11233,7 +11295,7 @@
       <c r="J40" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại 販売店 có số đăng ký doanh nghiệp phát hành hóa đơn hợp lệ để trống</t>
+・Tồn tại người đọc đã hủy đăng ký (số bản đọc 2→0) vào ngày áp dụng đó</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -11258,7 +11320,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
 </t>
           </r>
           <r>
@@ -11275,7 +11337,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận 販売店名 của dòng chi tiết</t>
+            <t>Kiểm tra dòng chi tiết của cửa hàng bán tương ứng</t>
           </r>
         </is>
       </c>
@@ -11318,7 +11380,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>販売店 có số đăng ký doanh nghiệp phát hành hóa đơn hợp lệ（`torihikisaki_no`）để trống được hiển thị với「（免）」gắn vào đầu 販売店名</t>
+            <t>・Số bản hiện tại **2**, số bản giảm **2**, số bản mới **0**, số bản tăng **0**</t>
           </r>
         </is>
       </c>
@@ -11364,7 +11426,11 @@
       <c r="BH40" s="45" t="inlineStr"/>
       <c r="BI40" s="10" t="n"/>
       <c r="BJ40" s="11" t="n"/>
-      <c r="BK40" s="46" t="inlineStr"/>
+      <c r="BK40" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
       <c r="BL40" s="10" t="n"/>
       <c r="BM40" s="10" t="n"/>
       <c r="BN40" s="10" t="n"/>
@@ -11372,20 +11438,20 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="144" customHeight="1">
+    <row r="41" ht="192" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-026</t>
+          <t>ACSMS-TC-029-046</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>Dấu khác biệt so với lần xuất trước</t>
+          <t>Đổi cửa hàng bán (giảm ở cửa hàng cũ / tăng ở cửa hàng mới)</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -11395,7 +11461,7 @@
       <c r="J41" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại 販売店 có giá trị khác với thời điểm xuất lần trước</t>
+・Tồn tại người đọc đã đổi cửa hàng bán từ A→B vào ngày áp dụng đó (số bản không đổi 1→1)</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -11420,7 +11486,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
 </t>
           </r>
           <r>
@@ -11437,7 +11503,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận dấu khác biệt của dòng chi tiết</t>
+            <t>Kiểm tra dòng chi tiết của cửa hàng cũ A và cửa hàng mới B</t>
           </r>
         </is>
       </c>
@@ -11480,7 +11546,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Dòng có chênh lệch so với giá trị tại thời điểm xuất lần trước được hiển thị kèm dấu khác biệt (`diff_mark=true`, trong báo cáo là「◆」)</t>
+            <t xml:space="preserve">・Cửa hàng cũ A: hiển thị số bản hiện tại **1** / số bản giảm **1** / số bản mới **0**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Cửa hàng mới B: hiển thị số bản hiện tại **0** / số bản tăng **1** / số bản mới **1**</t>
           </r>
         </is>
       </c>
@@ -11526,7 +11600,11 @@
       <c r="BH41" s="45" t="inlineStr"/>
       <c r="BI41" s="10" t="n"/>
       <c r="BJ41" s="11" t="n"/>
-      <c r="BK41" s="46" t="inlineStr"/>
+      <c r="BK41" s="46" t="inlineStr">
+        <is>
+          <t>Do chi nhánh quản lý của cửa hàng cũ không được lưu trong lịch sử, tạm thời tính vào chi nhánh quản lý của bản ghi cuối cùng trong ngày.</t>
+        </is>
+      </c>
       <c r="BL41" s="10" t="n"/>
       <c r="BM41" s="10" t="n"/>
       <c r="BN41" s="10" t="n"/>
@@ -11534,20 +11612,20 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="80" customHeight="1">
+    <row r="42" ht="160" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-027</t>
+          <t>ACSMS-TC-029-024</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>Loại trừ bản ghi có 現在部数 0 và 新部数 0</t>
+          <t>Hiển thị cột 委託</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -11557,7 +11635,7 @@
       <c r="J42" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại lịch sử có 現在部数=0 và 新部数=0</t>
+・Tồn tại 販売店 có 委託区分 là 日農委託・振込・その他</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -11582,7 +11660,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Nhập ngày áp dụng và thực hiện「レポートプレビュー」</t>
+            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận cột 委託 của dòng chi tiết</t>
           </r>
         </is>
       </c>
@@ -11608,7 +11703,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Bản ghi có 現在部数=0 và 新部数=0（`COALESCE(zenkai_dokusya_busu,0)=0 AND dokusya_busu=0`）không được hiển thị</t>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・販売店 có 委託区分 là 日農委託（`itaku_kubun=2`）hiển thị「委託」ở cột 委託
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・販売店 có 委託区分 là 振込（1）・その他（9）hiển thị cột 委託 để trống</t>
           </r>
         </is>
       </c>
@@ -11662,20 +11782,20 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="80" customHeight="1">
+    <row r="43" ht="144" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-028</t>
+          <t>ACSMS-TC-029-025</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="46" t="inlineStr">
         <is>
-          <t>Loại trừ 廃店</t>
+          <t>Hiển thị 販売店 miễn thuế</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -11685,7 +11805,7 @@
       <c r="J43" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại lịch sử của 廃店（haiten_flg=true）・販売店 dummy bản điện tử</t>
+・Tồn tại 販売店 có số đăng ký doanh nghiệp phát hành hóa đơn hợp lệ để trống</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -11710,7 +11830,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Nhập ngày áp dụng và thực hiện「レポートプレビュー」</t>
+            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận 販売店名 của dòng chi tiết</t>
           </r>
         </is>
       </c>
@@ -11736,7 +11873,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Bản ghi gắn với 廃店（haiten_flg=true）・販売店 dummy bản điện tử không được hiển thị</t>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>販売店 có số đăng ký doanh nghiệp phát hành hóa đơn hợp lệ（`torihikisaki_no`）để trống được hiển thị với「（免）」gắn vào đầu 販売店名</t>
           </r>
         </is>
       </c>
@@ -11796,14 +11950,14 @@
       </c>
       <c r="B44" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-029</t>
+          <t>ACSMS-TC-029-026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="46" t="inlineStr">
         <is>
-          <t>Tổng hợp 合計行</t>
+          <t>Dấu khác biệt so với lần xuất trước</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -11813,7 +11967,7 @@
       <c r="J44" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại nhiều 販売店 trong 1 chi nhánh quản lý</t>
+・Tồn tại 販売店 có giá trị khác với thời điểm xuất lần trước</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
@@ -11855,7 +12009,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Đối chiếu 合計行 và dòng chi tiết</t>
+            <t>Xác nhận dấu khác biệt của dòng chi tiết</t>
           </r>
         </is>
       </c>
@@ -11898,7 +12052,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>現在部数・増部数・減部数・新部数 của 合計行 khớp với tổng của từng dòng chi tiết trong chi nhánh quản lý tương ứng</t>
+            <t>Dòng có chênh lệch so với giá trị tại thời điểm xuất lần trước được hiển thị kèm dấu khác biệt (`diff_mark=true`, trong báo cáo là「◆」)</t>
           </r>
         </is>
       </c>
@@ -11952,20 +12106,20 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="128" customHeight="1">
+    <row r="45" ht="80" customHeight="1">
       <c r="A45" s="44" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-030</t>
+          <t>ACSMS-TC-029-027</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị mã chi nhánh quản lý phân cách bằng dấu gạch ngang</t>
+          <t>Loại trừ bản ghi có 現在部数 0 và 新部数 0</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -11975,7 +12129,7 @@
       <c r="J45" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại chi nhánh quản lý có mã chi nhánh quản lý 10 chữ số</t>
+・Tồn tại lịch sử có 現在部数=0 và 新部数=0</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
@@ -12000,24 +12154,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận hiển thị mã chi nhánh quản lý ở header của báo cáo</t>
+            <t>Nhập ngày áp dụng và thực hiện「レポートプレビュー」</t>
           </r>
         </is>
       </c>
@@ -12043,24 +12180,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Danh sách được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Mã chi nhánh quản lý 10 chữ số được hiển thị phân cách bằng dấu gạch ngang theo dạng 3-4-3 (ví dụ: 1AA-3300-001)</t>
+            <t>Bản ghi có 現在部数=0 và 新部数=0（`COALESCE(zenkai_dokusya_busu,0)=0 AND dokusya_busu=0`）không được hiển thị</t>
           </r>
         </is>
       </c>
@@ -12114,20 +12234,20 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="112" customHeight="1">
+    <row r="46" ht="80" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-031</t>
+          <t>ACSMS-TC-029-028</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>Đối tượng 0 bản ghi (preview)</t>
+          <t>Loại trừ 廃店</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -12137,7 +12257,7 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Không tồn tại dữ liệu đối tượng với điều kiện đã chỉ định</t>
+・Tồn tại lịch sử của 廃店（haiten_flg=true）・販売店 dummy bản điện tử</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -12162,7 +12282,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Thực hiện「レポートプレビュー」với 適用日・điều kiện không tồn tại đối tượng</t>
+            <t>Nhập ngày áp dụng và thực hiện「レポートプレビュー」</t>
           </r>
         </is>
       </c>
@@ -12188,15 +12308,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 200 (`reports:[]`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Message「対象のデータが存在しません。」được hiển thị (ACSMS-MSG-029-002, không phải toast)</t>
+            <t>Bản ghi gắn với 廃店（haiten_flg=true）・販売店 dummy bản điện tử không được hiển thị</t>
           </r>
         </is>
       </c>
@@ -12208,7 +12320,7 @@
       <c r="AD46" s="11" t="n"/>
       <c r="AE46" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -12250,20 +12362,20 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="176" customHeight="1">
+    <row r="47" ht="144" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-032</t>
+          <t>ACSMS-TC-029-029</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>Dialog xác nhận trước khi 電子帳票作成</t>
+          <t>Tổng hợp 合計行</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -12273,7 +12385,7 @@
       <c r="J47" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Tồn tại dữ liệu đối tượng ở ngày áp dụng</t>
+・Tồn tại nhiều 販売店 trong 1 chi nhánh quản lý</t>
         </is>
       </c>
       <c r="K47" s="10" t="n"/>
@@ -12298,7 +12410,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập ngày áp dụng và click nút「電子帳票作成」
+            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
 </t>
           </r>
           <r>
@@ -12315,7 +12427,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Click「いいえ」trên dialog xác nhận</t>
+            <t>Đối chiếu 合計行 và dòng chi tiết</t>
           </r>
         </is>
       </c>
@@ -12341,7 +12453,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Message xác nhận được hiển thị (message「増減通知を作成して日農担当者へメール送信を実行します。よろしいですか？」＝ACSMS-MSG-029-005)
+            <t xml:space="preserve">Danh sách được hiển thị
 </t>
           </r>
           <r>
@@ -12358,7 +12470,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xử lý bị hủy, và việc tạo PDF・gửi mail không được thực hiện</t>
+            <t>現在部数・増部数・減部数・新部数 của 合計行 khớp với tổng của từng dòng chi tiết trong chi nhánh quản lý tương ứng</t>
           </r>
         </is>
       </c>
@@ -12412,20 +12524,20 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="240" customHeight="1">
+    <row r="48" ht="128" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-033</t>
+          <t>ACSMS-TC-029-030</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>Xuất 電子帳票 (PDF)・lưu S3・thông báo mail (chi nhánh quản lý đơn lẻ)</t>
+          <t>Hiển thị mã chi nhánh quản lý phân cách bằng dấu gạch ngang</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -12435,7 +12547,7 @@
       <c r="J48" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・適用日・điều kiện chỉ tương ứng 1 chi nhánh quản lý đối tượng</t>
+・Tồn tại chi nhánh quản lý có mã chi nhánh quản lý 10 chữ số</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -12460,7 +12572,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn 適用日・管理支店 và thực hiện「電子帳票作成」, click「はい」trên dialog xác nhận</t>
+            <t xml:space="preserve">Nhập ngày áp dụng và thực hiện「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận hiển thị mã chi nhánh quản lý ở header của báo cáo</t>
           </r>
         </is>
       </c>
@@ -12486,40 +12615,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 200
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・File PDF được tải xuống (`Content-Type: application/pdf`, tên file `増減通知_{管理支店コード}_{適用日YYYYMMDD}.pdf`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PDF đã tạo được lưu vào S3
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Mail hoàn tất tạo 増減通知 được gửi đến người phụ trách 日農 (tiền tố tiêu đề `【AgriNews_ACSMS】`, nội dung không chứa thông tin cá nhân)</t>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Mã chi nhánh quản lý 10 chữ số được hiển thị phân cách bằng dấu gạch ngang theo dạng 3-4-3 (ví dụ: 1AA-3300-001)</t>
           </r>
         </is>
       </c>
@@ -12573,20 +12686,20 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="448" customHeight="1">
+    <row r="49" ht="112" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>34</v>
       </c>
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-034</t>
+          <t>ACSMS-TC-029-031</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>Xuất ZIP nhiều chi nhánh quản lý・lịch sử・log thao tác</t>
+          <t>Đối tượng 0 bản ghi (preview)</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -12596,7 +12709,7 @@
       <c r="J49" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・適用日・điều kiện tương ứng nhiều chi nhánh quản lý đối tượng</t>
+・Không tồn tại dữ liệu đối tượng với điều kiện đã chỉ định</t>
         </is>
       </c>
       <c r="K49" s="10" t="n"/>
@@ -12621,112 +12734,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn 適用日・nhiều 管理支店 và thực hiện「電子帳票作成」, click「はい」trên dialog xác nhận
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Thực hiện query sau trên DB, xác nhận lịch sử tải xuống và log thao tác
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_file_download
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY download_datetime DESC;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減通知（日本農業新聞）出力画面 (ACSMS-SCR-029)'
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>Thực hiện「レポートプレビュー」với 適用日・điều kiện không tồn tại đối tượng</t>
           </r>
         </is>
       </c>
@@ -12752,32 +12760,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・File ZIP gộp PDF của từng chi nhánh quản lý được tải xuống (`Content-Type: application/zip`, tên file `増減通知_{適用日YYYYMMDD}.zip`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Lịch sử được đăng ký vào t_file_download theo từng file PDF (download_type=4, target_month là năm tháng của ngày áp dụng)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・1 bản ghi audit log được ghi vào t_log (log_type=1, operation=`EXPORT_PDF`, result_status=1, target_table=`t_file_download`)</t>
+            <t xml:space="preserve">・Trả về HTTP 200 (`reports:[]`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Message「対象のデータが存在しません。」được hiển thị (ACSMS-MSG-029-002, không phải toast)</t>
           </r>
         </is>
       </c>
@@ -12789,7 +12780,7 @@
       <c r="AD49" s="11" t="n"/>
       <c r="AE49" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF49" s="11" t="n"/>
@@ -12831,20 +12822,20 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="208" customHeight="1">
+    <row r="50" ht="176" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>35</v>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-035</t>
+          <t>ACSMS-TC-029-032</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>Đối tượng 0 bản ghi (電子帳票作成)</t>
+          <t>Dialog xác nhận trước khi 電子帳票作成</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -12854,7 +12845,7 @@
       <c r="J50" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Không tồn tại dữ liệu đối tượng với điều kiện đã chỉ định</t>
+・Tồn tại dữ liệu đối tượng ở ngày áp dụng</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -12879,7 +12870,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện「電子帳票作成」với 適用日・điều kiện không tồn tại đối tượng, click「はい」trên dialog xác nhận
+            <t xml:space="preserve">Nhập ngày áp dụng và click nút「電子帳票作成」
 </t>
           </r>
           <r>
@@ -12896,7 +12887,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận số bản ghi đăng ký của t_file_download trên DB</t>
+            <t>Click「いいえ」trên dialog xác nhận</t>
           </r>
         </is>
       </c>
@@ -12922,23 +12913,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 200 (`{ data: { reports: [] } }` của `application/json`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・File PDF／ZIP không được tải xuống
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Message「対象のデータが存在しません。」được hiển thị (ACSMS-MSG-029-002)
+            <t xml:space="preserve">Message xác nhận được hiển thị (message「増減通知を作成して日農担当者へメール送信を実行します。よろしいですか？」＝ACSMS-MSG-029-005)
 </t>
           </r>
           <r>
@@ -12955,7 +12930,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Bản ghi không được đăng ký vào t_file_download</t>
+            <t>Xử lý bị hủy, và việc tạo PDF・gửi mail không được thực hiện</t>
           </r>
         </is>
       </c>
@@ -12967,7 +12942,7 @@
       <c r="AD50" s="11" t="n"/>
       <c r="AE50" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF50" s="11" t="n"/>
@@ -13009,20 +12984,20 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="224" customHeight="1">
+    <row r="51" ht="240" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>36</v>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-036</t>
+          <t>ACSMS-TC-029-033</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>Rollback transaction</t>
+          <t>Xuất 電子帳票 (PDF)・lưu S3・thông báo mail (chi nhánh quản lý đơn lẻ)</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -13032,7 +13007,7 @@
       <c r="J51" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Đã chuẩn bị sẵn để phát sinh lỗi DB khi đăng ký lịch sử tải xuống</t>
+・適用日・điều kiện chỉ tương ứng 1 chi nhánh quản lý đối tượng</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -13057,24 +13032,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện「電子帳票作成」(inject lỗi giữa chừng quá trình đăng ký DB)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận trạng thái của t_file_download・t_log trên DB</t>
+            <t>Chọn 適用日・管理支店 và thực hiện「電子帳票作成」, click「はい」trên dialog xác nhận</t>
           </r>
         </is>
       </c>
@@ -13100,32 +13058,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Cả t_file_download・t_log（log_type=1）đều không được đăng ký (được rollback)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・1 bản ghi error log được ghi vào t_log (log_type=3, result_status=2)</t>
+            <t xml:space="preserve">・Trả về HTTP 200
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File PDF được tải xuống (`Content-Type: application/pdf`, tên file `増減通知_{管理支店コード}_{適用日YYYYMMDD}.pdf`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PDF đã tạo được lưu vào S3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Mail hoàn tất tạo 増減通知 được gửi đến người phụ trách 日農 (tiền tố tiêu đề `【AgriNews_ACSMS】`, nội dung không chứa thông tin cá nhân)</t>
           </r>
         </is>
       </c>
@@ -13137,7 +13103,7 @@
       <c r="AD51" s="11" t="n"/>
       <c r="AE51" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF51" s="11" t="n"/>
@@ -13171,12 +13137,7 @@
       <c r="BH51" s="45" t="inlineStr"/>
       <c r="BI51" s="10" t="n"/>
       <c r="BJ51" s="11" t="n"/>
-      <c r="BK51" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK51" s="46" t="inlineStr"/>
       <c r="BL51" s="10" t="n"/>
       <c r="BM51" s="10" t="n"/>
       <c r="BN51" s="10" t="n"/>
@@ -13184,74 +13145,257 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>カテゴリ5: Xử lý lỗi chung (Common Error Handling)</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
+    <row r="52" ht="448" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-034</t>
+        </is>
+      </c>
       <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>Xuất ZIP nhiều chi nhánh quản lý・lịch sử・log thao tác</t>
+        </is>
+      </c>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・適用日・điều kiện tương ứng nhiều chi nhánh quản lý đối tượng</t>
+        </is>
+      </c>
       <c r="K52" s="10" t="n"/>
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="10" t="n"/>
       <c r="N52" s="10" t="n"/>
       <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chọn 適用日・nhiều 管理支店 và thực hiện「電子帳票作成」, click「はい」trên dialog xác nhận
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện query sau trên DB, xác nhận lịch sử tải xuống và log thao tác
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_file_download
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY download_datetime DESC;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減通知（日本農業新聞）出力画面 (ACSMS-SCR-029)'
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
+          </r>
+        </is>
+      </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File ZIP gộp PDF của từng chi nhánh quản lý được tải xuống (`Content-Type: application/zip`, tên file `増減通知_{適用日YYYYMMDD}.zip`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Lịch sử được đăng ký vào t_file_download theo từng file PDF (download_type=4, target_month là năm tháng của ngày áp dụng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・1 bản ghi audit log được ghi vào t_log (log_type=1, operation=`EXPORT_PDF`, result_status=1, target_table=`t_file_download`)</t>
+          </r>
+        </is>
+      </c>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="10" t="n"/>
       <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
       <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
       <c r="AK52" s="10" t="n"/>
-      <c r="AL52" s="10" t="n"/>
-      <c r="AM52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
       <c r="AN52" s="10" t="n"/>
-      <c r="AO52" s="10" t="n"/>
-      <c r="AP52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
       <c r="AQ52" s="10" t="n"/>
-      <c r="AR52" s="10" t="n"/>
-      <c r="AS52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
       <c r="AT52" s="10" t="n"/>
-      <c r="AU52" s="10" t="n"/>
-      <c r="AV52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
       <c r="AW52" s="10" t="n"/>
-      <c r="AX52" s="10" t="n"/>
-      <c r="AY52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
       <c r="AZ52" s="10" t="n"/>
-      <c r="BA52" s="10" t="n"/>
-      <c r="BB52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
       <c r="BC52" s="10" t="n"/>
-      <c r="BD52" s="10" t="n"/>
-      <c r="BE52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
       <c r="BF52" s="10" t="n"/>
-      <c r="BG52" s="10" t="n"/>
-      <c r="BH52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
       <c r="BI52" s="10" t="n"/>
-      <c r="BJ52" s="10" t="n"/>
-      <c r="BK52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr"/>
       <c r="BL52" s="10" t="n"/>
       <c r="BM52" s="10" t="n"/>
       <c r="BN52" s="10" t="n"/>
@@ -13259,20 +13403,20 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="112" customHeight="1">
+    <row r="53" ht="208" customHeight="1">
       <c r="A53" s="44" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-037</t>
+          <t>ACSMS-TC-029-035</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>Tham số request không hợp lệ (BAD_REQUEST)</t>
+          <t>Đối tượng 0 bản ghi (電子帳票作成)</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -13281,7 +13425,8 @@
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="46" t="inlineStr">
         <is>
-          <t>・Đã đăng nhập bằng CHUOKAI</t>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Không tồn tại dữ liệu đối tượng với điều kiện đã chỉ định</t>
         </is>
       </c>
       <c r="K53" s="10" t="n"/>
@@ -13306,7 +13451,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi GET「/api/v1/report/zougen-nichino/preview?tekiyo_date=2026-03-01&amp;kanri_shiten_id=abc」(chuỗi ký tự ở mục số) qua tab Network của DevTools</t>
+            <t xml:space="preserve">Thực hiện「電子帳票作成」với 適用日・điều kiện không tồn tại đối tượng, click「はい」trên dialog xác nhận
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận số bản ghi đăng ký của t_file_download trên DB</t>
           </r>
         </is>
       </c>
@@ -13332,7 +13494,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。` hoặc `error_code: VALIDATION_ERROR`)</t>
+            <t xml:space="preserve">・Trả về HTTP 200 (`{ data: { reports: [] } }` của `application/json`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File PDF／ZIP không được tải xuống
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Message「対象のデータが存在しません。」được hiển thị (ACSMS-MSG-029-002)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bản ghi không được đăng ký vào t_file_download</t>
           </r>
         </is>
       </c>
@@ -13386,20 +13581,20 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="176" customHeight="1">
+    <row r="54" ht="224" customHeight="1">
       <c r="A54" s="44" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-038</t>
+          <t>ACSMS-TC-029-036</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>Session hết hạn (UNAUTHORIZED)</t>
+          <t>Rollback transaction</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -13409,7 +13604,7 @@
       <c r="J54" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Đã chuẩn bị sẵn để buộc hết hạn session bằng công cụ quản trị</t>
+・Đã chuẩn bị sẵn để phát sinh lỗi DB khi đăng ký lịch sử tải xuống</t>
         </is>
       </c>
       <c r="K54" s="10" t="n"/>
@@ -13434,7 +13629,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Buộc hết hạn session khi đang mở màn hình 増減通知（日本農業新聞）出力
+            <t xml:space="preserve">Thực hiện「電子帳票作成」(inject lỗi giữa chừng quá trình đăng ký DB)
 </t>
           </r>
           <r>
@@ -13451,7 +13646,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Click nút「レポートプレビュー」</t>
+            <t>Xác nhận trạng thái của t_file_download・t_log trên DB</t>
           </r>
         </is>
       </c>
@@ -13477,7 +13672,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Màn hình đang ở trạng thái được hiển thị
+            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
 </t>
           </r>
           <r>
@@ -13494,15 +13689,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Chuyển đến「/login」(có gắn `redirect` vào query)</t>
+            <t xml:space="preserve">・Cả t_file_download・t_log（log_type=1）đều không được đăng ký (được rollback)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・1 bản ghi error log được ghi vào t_log (log_type=3, result_status=2)</t>
           </r>
         </is>
       </c>
@@ -13548,7 +13743,12 @@
       <c r="BH54" s="45" t="inlineStr"/>
       <c r="BI54" s="10" t="n"/>
       <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BK54" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL54" s="10" t="n"/>
       <c r="BM54" s="10" t="n"/>
       <c r="BN54" s="10" t="n"/>
@@ -13556,134 +13756,74 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="144" customHeight="1">
-      <c r="A55" s="44" t="n">
-        <v>39</v>
-      </c>
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-029-039</t>
-        </is>
-      </c>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ5: Xử lý lỗi chung (Common Error Handling)</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="46" t="inlineStr">
-        <is>
-          <t>Hình dạng response lỗi validation (VALIDATION_ERROR)</t>
-        </is>
-      </c>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="46" t="inlineStr">
-        <is>
-          <t>・Đã đăng nhập bằng CHUOKAI</t>
-        </is>
-      </c>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Gửi POST「/api/v1/report/zougen-nichino/export」với request body thiếu tekiyo_date qua tab Network của DevTools</t>
-          </r>
-        </is>
-      </c>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="10" t="n"/>
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="X55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Response có chứa mảng `errors`, và mỗi phần tử có hình dạng `{ field, message }`</t>
-          </r>
-        </is>
-      </c>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="10" t="n"/>
       <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="11" t="n"/>
-      <c r="AE55" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF55" s="11" t="n"/>
-      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
       <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="11" t="n"/>
-      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="10" t="n"/>
-      <c r="AL55" s="11" t="n"/>
-      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AL55" s="10" t="n"/>
+      <c r="AM55" s="10" t="n"/>
       <c r="AN55" s="10" t="n"/>
-      <c r="AO55" s="11" t="n"/>
-      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AO55" s="10" t="n"/>
+      <c r="AP55" s="10" t="n"/>
       <c r="AQ55" s="10" t="n"/>
-      <c r="AR55" s="11" t="n"/>
-      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AR55" s="10" t="n"/>
+      <c r="AS55" s="10" t="n"/>
       <c r="AT55" s="10" t="n"/>
-      <c r="AU55" s="11" t="n"/>
-      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AU55" s="10" t="n"/>
+      <c r="AV55" s="10" t="n"/>
       <c r="AW55" s="10" t="n"/>
-      <c r="AX55" s="11" t="n"/>
-      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AX55" s="10" t="n"/>
+      <c r="AY55" s="10" t="n"/>
       <c r="AZ55" s="10" t="n"/>
-      <c r="BA55" s="11" t="n"/>
-      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BA55" s="10" t="n"/>
+      <c r="BB55" s="10" t="n"/>
       <c r="BC55" s="10" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BD55" s="10" t="n"/>
+      <c r="BE55" s="10" t="n"/>
       <c r="BF55" s="10" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BG55" s="10" t="n"/>
+      <c r="BH55" s="10" t="n"/>
       <c r="BI55" s="10" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="46" t="inlineStr"/>
+      <c r="BJ55" s="10" t="n"/>
+      <c r="BK55" s="10" t="n"/>
       <c r="BL55" s="10" t="n"/>
       <c r="BM55" s="10" t="n"/>
       <c r="BN55" s="10" t="n"/>
@@ -13691,20 +13831,20 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="160" customHeight="1">
+    <row r="56" ht="112" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>40</v>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-040</t>
+          <t>ACSMS-TC-029-037</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="46" t="inlineStr">
         <is>
-          <t>Vượt giới hạn rate (TOO_MANY_REQUESTS)</t>
+          <t>Tham số request không hợp lệ (BAD_REQUEST)</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -13738,24 +13878,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Gửi liên tục request tương đương preview hoặc 電子帳票作成 đến số lần giới hạn
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Gửi thêm request vượt quá giới hạn</t>
+            <t>Gửi GET「/api/v1/report/zougen-nichino/preview?tekiyo_date=2026-03-01&amp;kanri_shiten_id=abc」(chuỗi ký tự ở mục số) qua tab Network của DevTools</t>
           </r>
         </is>
       </c>
@@ -13781,24 +13904,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Các request đến số lần giới hạn được xử lý bình thường
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)</t>
+            <t>Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。` hoặc `error_code: VALIDATION_ERROR`)</t>
           </r>
         </is>
       </c>
@@ -13852,20 +13958,20 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="160" customHeight="1">
+    <row r="57" ht="176" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>41</v>
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-041</t>
+          <t>ACSMS-TC-029-038</t>
         </is>
       </c>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>Lỗi hệ thống (INTERNAL_SERVER_ERROR)</t>
+          <t>Session hết hạn (UNAUTHORIZED)</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -13875,7 +13981,7 @@
       <c r="J57" s="46" t="inlineStr">
         <is>
           <t>・Đã đăng nhập bằng CHUOKAI
-・Đã chuẩn bị sẵn để phát sinh exception ở phía server</t>
+・Đã chuẩn bị sẵn để buộc hết hạn session bằng công cụ quản trị</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -13900,7 +14006,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Thực hiện「レポートプレビュー」ở trạng thái đã phát sinh lỗi kết nối DB v.v. ở phía server</t>
+            <t xml:space="preserve">Buộc hết hạn session khi đang mở màn hình 増減通知（日本農業新聞）出力
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Click nút「レポートプレビュー」</t>
           </r>
         </is>
       </c>
@@ -13926,15 +14049,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Message「システムエラーが発生しました。しばらくしてから再度お試しください。」được hiển thị (ACSMS-MSG-029-003)</t>
+            <t xml:space="preserve">Màn hình đang ở trạng thái được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Chuyển đến「/login」(có gắn `redirect` vào query)</t>
           </r>
         </is>
       </c>
@@ -13988,20 +14128,20 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="128" customHeight="1">
+    <row r="58" ht="144" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>42</v>
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-042</t>
+          <t>ACSMS-TC-029-039</t>
         </is>
       </c>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>Ngắt kết nối mạng</t>
+          <t>Hình dạng response lỗi validation (VALIDATION_ERROR)</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -14035,24 +14175,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「Offline」ở tab Network của DevTools và ngắt kết nối mạng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Click nút「レポートプレビュー」</t>
+            <t>Gửi POST「/api/v1/report/zougen-nichino/export」với request body thiếu tekiyo_date qua tab Network của DevTools</t>
           </r>
         </is>
       </c>
@@ -14078,32 +14201,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mạng bị ngắt kết nối
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Toast lỗi mạng được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Không kết thúc bất thường</t>
+            <t xml:space="preserve">・Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Response có chứa mảng `errors`, và mỗi phần tử có hình dạng `{ field, message }`</t>
           </r>
         </is>
       </c>
@@ -14157,20 +14263,20 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
-    <row r="59" ht="192" customHeight="1">
+    <row r="59" ht="160" customHeight="1">
       <c r="A59" s="44" t="n">
         <v>43</v>
       </c>
       <c r="B59" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-043</t>
+          <t>ACSMS-TC-029-040</t>
         </is>
       </c>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>An toàn với input SQL injection</t>
+          <t>Vượt giới hạn rate (TOO_MANY_REQUESTS)</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -14204,7 +14310,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Gửi GET「/api/v1/report/zougen-nichino/preview」với tekiyo_date chỉ định `2026-03-01'; DROP TABLE t_dokusya_rireki; --` qua tab Network của DevTools
+            <t xml:space="preserve">Gửi liên tục request tương đương preview hoặc 電子帳票作成 đến số lần giới hạn
 </t>
           </r>
           <r>
@@ -14221,7 +14327,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận bảng t_dokusya_rireki tồn tại trên DB</t>
+            <t>Gửi thêm request vượt quá giới hạn</t>
           </r>
         </is>
       </c>
@@ -14247,15 +14353,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Giá trị input được xử lý như literal bởi parameterized query, và không được thực thi như SQL
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Trả về HTTP 400 (`error_code: VALIDATION_ERROR` hoặc `BAD_REQUEST`)
+            <t xml:space="preserve">Các request đến số lần giới hạn được xử lý bình thường
 </t>
           </r>
           <r>
@@ -14272,7 +14370,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Bảng t_dokusya_rireki không bị xóa và tồn tại</t>
+            <t>Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)</t>
           </r>
         </is>
       </c>
@@ -14326,10 +14424,1132 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
+    <row r="60" ht="160" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-041</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>Lỗi hệ thống (INTERNAL_SERVER_ERROR)</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Đã chuẩn bị sẵn để phát sinh exception ở phía server</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Thực hiện「レポートプレビュー」ở trạng thái đã phát sinh lỗi kết nối DB v.v. ở phía server</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Message「システムエラーが発生しました。しばらくしてから再度お試しください。」được hiển thị (ACSMS-MSG-029-003)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="128" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-042</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>Ngắt kết nối mạng</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chọn「Offline」ở tab Network của DevTools và ngắt kết nối mạng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Click nút「レポートプレビュー」</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Mạng bị ngắt kết nối
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Toast lỗi mạng được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Không kết thúc bất thường</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="192" customHeight="1">
+      <c r="A62" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-043</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>An toàn với input SQL injection</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi GET「/api/v1/report/zougen-nichino/preview」với tekiyo_date chỉ định `2026-03-01'; DROP TABLE t_dokusya_rireki; --` qua tab Network của DevTools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận bảng t_dokusya_rireki tồn tại trên DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Giá trị input được xử lý như literal bởi parameterized query, và không được thực thi như SQL
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trả về HTTP 400 (`error_code: VALIDATION_ERROR` hoặc `BAD_REQUEST`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bảng t_dokusya_rireki không bị xóa và tồn tại</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="45" t="inlineStr"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="45" t="inlineStr"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="11" t="n"/>
+      <c r="AM62" s="45" t="inlineStr"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="11" t="n"/>
+      <c r="AP62" s="45" t="inlineStr"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="11" t="n"/>
+      <c r="AS62" s="45" t="inlineStr"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="11" t="n"/>
+      <c r="AV62" s="45" t="inlineStr"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="11" t="n"/>
+      <c r="AY62" s="45" t="inlineStr"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="11" t="n"/>
+      <c r="BB62" s="45" t="inlineStr"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="11" t="n"/>
+      <c r="BE62" s="45" t="inlineStr"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="11" t="n"/>
+      <c r="BH62" s="45" t="inlineStr"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="11" t="n"/>
+      <c r="BK62" s="46" t="inlineStr"/>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="450" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-047</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Phân trang (15 dòng cửa hàng bán/trang・API riêng・khớp với PDF)</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại từ 16 người đọc thuộc đối tượng tăng giảm trở lên vào ngày áp dụng đó</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chuyển sang trang 2 bằng pager ở dưới phần preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Thực thi「電子帳票作成」với cùng điều kiện và kiểm tra cấu trúc trang của PDF xuất ra</t>
+          </r>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trang 1 hiển thị tối đa **15 dòng cửa hàng bán** (≒15 người đọc. Phần lớn là 1 dòng/người đọc. Do đổi cửa hàng bán có thể thành 2 dòng nên không chính xác đúng 15 dòng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Pager (tổng N bản ghi ＝ số người đọc thuộc đối tượng・trang 1/M) được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「Page」ở header báo biểu là `1/M`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・BE chỉ load chi tiết của số người đọc trong 1 trang bằng `COUNT(DISTINCT dokusya_id)` ＋ OFFSET/LIMIT trên `dokusya_id` (không load toàn bộ)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Lấy lại trang 2 bằng API riêng và hiển thị những người đọc còn lại (trình duyệt chỉ vẽ 1 trang)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「Page」được cập nhật thành `2/M`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Trang thứ n của PDF xuất ra có cùng nội dung・cùng vị trí ngắt trang với trang thứ n của preview (gộp toàn bộ chi nhánh quản lý vào 1 PDF, chỉ ngắt trang ở đầu trang)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr">
+        <is>
+          <t>Tổng của mỗi chi nhánh quản lý được tính từ các dòng trong trang đó (nếu chi nhánh quản lý trải qua nhiều trang thì là tổng trong trang).</t>
+        </is>
+      </c>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: Đối tượng tổng hợp (Scope)</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="10" t="n"/>
+      <c r="AM64" s="10" t="n"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="10" t="n"/>
+      <c r="AP64" s="10" t="n"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="10" t="n"/>
+      <c r="AS64" s="10" t="n"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="10" t="n"/>
+      <c r="AV64" s="10" t="n"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="10" t="n"/>
+      <c r="AY64" s="10" t="n"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="10" t="n"/>
+      <c r="BB64" s="10" t="n"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="10" t="n"/>
+      <c r="BE64" s="10" t="n"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="10" t="n"/>
+      <c r="BH64" s="10" t="n"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="10" t="n"/>
+      <c r="BK64" s="10" t="n"/>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="450" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-048</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>Giới hạn đối tượng tổng hợp chỉ bản giấy (#56410)</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `report.export_zougen_nichino`)
+・Lấy ngày áp dụng là 2026/09/01, chuẩn bị người đọc có lịch sử thuộc đối tượng báo cáo tăng giảm (`zougen_hokoku_flg = true`) trong cùng ngày như sau (tất cả đều thuộc cửa hàng bán A có thật・cùng chi nhánh quản lý)
+・(a) Bản giấy (dokusya_shubetsu=1) tăng từ 1 → 3 bản, 1 người
+・(b) Kết hợp (3) có thay đổi số bản, 1 người
+・(c) Bản điện tử (2)・đã duyệt (denshi_shonin_status=1) 1 người
+・(d) Bản điện tử (2)・chưa duyệt 1 người</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Hiển thị preview với ngày áp dụng 2026/09/01 và kiểm tra dòng cửa hàng bán cùng số bản được tổng hợp
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất PDF và kiểm tra số bản tăng・số bản giảm・chênh lệch của cửa hàng bán A
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra biến động của (b) kết hợp có được phản ánh vào số bản không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra biến động của (c) bản điện tử・đã duyệt có được phản ánh vào số bản không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất ở trạng thái chỉ giữ lại (a) và xóa các trường hợp còn lại, xác nhận số bản không đổi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xuất phiếu liên lạc tăng giảm (cửa hàng bán) SCR-028 với cùng điều kiện và xác nhận người đọc thuộc đối tượng khớp nhau</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Số bản tăng của cửa hàng bán A **chỉ gồm phần tăng của (a) (+2 bản)**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Giá trị trong PDF khớp với preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**Không được phản ánh**. Báo biểu này cũng truyền đạt tăng giảm số bản, mà kết hợp không kèm việc giao báo nên nằm ngoài đối tượng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**Không được phản ánh**. Điều kiện cũ "bản điện tử chỉ tổng hợp khi đã duyệt" đã bị bỏ vì nằm gọn trong giới hạn chỉ bản giấy (yêu cầu khách hàng 2026-08 / #56410)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nội dung xuất ra không thay đổi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Người đọc thuộc đối tượng của hai báo biểu khớp nhau
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cùng phương châm với phiếu liên lạc tăng giảm (cửa hàng bán) SCR-028, nhưng **điều kiện do từng màn tự giữ** (không dùng chung nên nếu chỉ sửa một bên sẽ lệch nhau). ステップ6 là để phát hiện sự lệch đó
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Màn hình này không có ô nhập cửa hàng bán trong điều kiện xuất nên việc điều khiển hiển thị cửa hàng dummy (#56597) nằm ngoài phạm vi. Tuy vậy phía SQL tổng hợp vẫn loại cửa hàng ngừng kinh doanh・cửa hàng dummy bằng `h.haiten_flg = false`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Danh sách người đọc (SCR-026) có đối tượng khác nhau theo loại báo biểu (theo chi nhánh quản lý thì kết hợp・bản điện tử cũng thuộc đối tượng). Không được dùng lại nguyên điều kiện của màn hình này</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="802">
+  <mergeCells count="888">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
@@ -14338,12 +15558,16 @@
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
@@ -14353,6 +15577,7 @@
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -14380,6 +15605,7 @@
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -14390,15 +15616,17 @@
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AG37:AI37"/>
+    <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="BK37:BQ37"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
@@ -14406,9 +15634,12 @@
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
@@ -14420,12 +15651,13 @@
     <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
-    <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -14440,6 +15672,7 @@
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
@@ -14458,16 +15691,14 @@
     <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
     <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AG55:AI55"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BK28:BQ28"/>
     <mergeCell ref="AY32:BA32"/>
     <mergeCell ref="BB33:BD33"/>
@@ -14481,6 +15712,7 @@
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -14491,12 +15723,16 @@
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
+    <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
@@ -14509,6 +15745,7 @@
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -14522,7 +15759,6 @@
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
-    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="BH46:BJ46"/>
@@ -14530,6 +15766,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14544,6 +15781,7 @@
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -14552,6 +15790,7 @@
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
@@ -14560,8 +15799,10 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
+    <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY53:BA53"/>
@@ -14570,11 +15811,12 @@
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
-    <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
@@ -14583,6 +15825,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14598,6 +15841,7 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
@@ -14610,6 +15854,7 @@
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
@@ -14617,35 +15862,44 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="AV55:AX55"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AV52:AX52"/>
     <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AV45:AX45"/>
@@ -14655,6 +15909,7 @@
     <mergeCell ref="AV26:AX26"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AM42:AO42"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="BB19:BD19"/>
@@ -14662,14 +15917,15 @@
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AV27:AX27"/>
-    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -14677,7 +15933,7 @@
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
-    <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -14689,6 +15945,7 @@
     <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="AE44:AF44"/>
@@ -14696,6 +15953,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14719,7 +15977,6 @@
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
-    <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="AY14:BA14"/>
@@ -14749,17 +16006,22 @@
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
+    <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -14767,16 +16029,21 @@
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
+    <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
@@ -14786,9 +16053,11 @@
     <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -14806,7 +16075,6 @@
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
     <mergeCell ref="BH27:BJ27"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
@@ -14819,7 +16087,9 @@
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
@@ -14848,18 +16118,24 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14877,13 +16153,16 @@
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="A64:BQ64"/>
     <mergeCell ref="AE10:AF11"/>
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14900,8 +16179,9 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="AJ55:AL55"/>
+    <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
@@ -14911,7 +16191,6 @@
     <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
-    <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
     <mergeCell ref="E27:I27"/>
     <mergeCell ref="AS49:AU49"/>
@@ -14919,6 +16198,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="A35:BQ35"/>
@@ -14928,6 +16208,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14935,6 +16216,8 @@
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -14969,28 +16252,31 @@
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
-    <mergeCell ref="A52:BQ52"/>
     <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
-    <mergeCell ref="BB55:BD55"/>
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
+    <mergeCell ref="AS52:AU52"/>
     <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="X44:AD44"/>
     <mergeCell ref="AP34:AR34"/>
@@ -15003,6 +16289,7 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
@@ -15016,12 +16303,16 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A55:BQ55"/>
     <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
+    <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -15029,7 +16320,9 @@
     <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -15037,6 +16330,7 @@
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -15044,10 +16338,12 @@
     <mergeCell ref="AE25:AF25"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
+    <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -15056,12 +16352,15 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -15080,11 +16379,13 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AP52:AR52"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
@@ -15093,6 +16394,7 @@
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
@@ -15103,9 +16405,9 @@
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
-    <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -15123,22 +16425,25 @@
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE34 AE36:AE51 AE53:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE34 AE36:AE54 AE56:AE63 AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG34 AG36:AG51 AG53:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG34 AG36:AG54 AG56:AG63 AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV34 AV36:AV51 AV53:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV34 AV36:AV54 AV56:AV63 AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
